--- a/AAII_Financials/Quarterly/UNICY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UNICY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>UNICY</t>
   </si>
@@ -656,123 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -809,47 +813,50 @@
       <c r="N8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="3">
         <v>1728700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1486100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1464200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1357000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1448500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1405400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1432900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1290500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1414700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1386000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1473700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1619200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1669400</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -886,47 +893,50 @@
       <c r="N9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3">
         <v>1126600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>933300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>920000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>849700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>903600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>833900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>837200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>765500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>853200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>813100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>875600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>981800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1046400</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -963,47 +973,50 @@
       <c r="N10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="3">
         <v>602000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>552800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>544200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>507400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>544900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>571400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>595600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>524900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>561500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>572900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>598100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>637400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>623100</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1031,8 +1044,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,47 +1083,50 @@
       <c r="N12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3">
         <v>16100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>15800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>14500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>16000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>16400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,8 +1202,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,14 +1243,14 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
@@ -1247,23 +1267,26 @@
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3">
         <v>-800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>137700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1300,47 +1323,50 @@
       <c r="N15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="3">
         <v>16900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>18100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>18400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>19800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>19300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>19400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>20700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>20400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>21700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>23600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1365,8 +1391,9 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1403,47 +1430,50 @@
       <c r="N17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="3">
         <v>1545400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1262300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1300500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1157600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1313200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1145100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1213300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1059200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1253000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1121400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1392300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1354600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1664300</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1480,47 +1510,50 @@
       <c r="N18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3">
         <v>183300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>223800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>163700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>199400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>135300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>260300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>219500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>231200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>161700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>264600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>81400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>264600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1548,8 +1581,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1586,47 +1620,50 @@
       <c r="N20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P20" s="3">
         <v>-10800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>11400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>8200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>14000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1663,47 +1700,50 @@
       <c r="N21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3">
         <v>252400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>288200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>242700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>268700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>205400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>335000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>294900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>307900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>236200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>331300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>171100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>327600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1740,8 +1780,8 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1779,8 +1819,11 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1817,47 +1860,50 @@
       <c r="N23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="3">
         <v>172500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>223600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>172500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>204400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>139600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>266000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>224400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>242600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>169900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>261600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>95400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>245900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1894,47 +1940,50 @@
       <c r="N24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="3">
         <v>52100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>65400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>56800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>75100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>56000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>80600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>58100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>79000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>63100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>75600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>70600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>58900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2010,8 +2059,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2048,47 +2100,50 @@
       <c r="N26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="3">
         <v>120400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>158200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>115700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>129200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>83700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>185400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>166300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>163600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>106800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>186000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>24800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>187000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2125,47 +2180,50 @@
       <c r="N27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="3">
         <v>107500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>132100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>100700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>111700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>74200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>158500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>146000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>142500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>89900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>162000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>169300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2241,8 +2299,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2279,8 +2340,8 @@
       <c r="N29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2318,8 +2379,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2395,8 +2459,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2472,8 +2539,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2510,47 +2580,50 @@
       <c r="N32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="3">
         <v>10800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-11400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-8200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>18700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2587,47 +2660,50 @@
       <c r="N33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="3">
         <v>107500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>132100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>100700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>111700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>74200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>158500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>146000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>142500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>89900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>162000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>169300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2703,8 +2779,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2741,129 +2820,135 @@
       <c r="N35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="3">
         <v>107500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>132100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>100700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>111700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>74200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>158500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>146000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>142500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>89900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>162000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>169300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2891,8 +2976,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2920,85 +3006,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1565500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1614200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1843900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1660400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1425700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1333800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1262600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1685600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1262600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1685600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1659700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1541800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1422500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1631300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1482700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1288400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1347400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1584200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1492200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1462500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1425800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1443400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1273800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1134600</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3036,585 +3126,609 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>642200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>800800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>861100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>750600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>822700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>821200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>738900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>689400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>715300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>630200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>763600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>757100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>761300</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900400</v>
+      </c>
+      <c r="E43" s="3">
         <v>987100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1040000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1072600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1083400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>964900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1075200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>946600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>939200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>946600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>939200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>947400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1086100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>881100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>895500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>812000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>888800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>809000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>802200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>767000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>826100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>783100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>851100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>910600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1072900</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>772800</v>
+      </c>
+      <c r="E44" s="3">
         <v>786700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>822100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>770500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>684200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>682300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>730400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>777400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>791400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>777400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>791400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>879200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>834900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>815900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>771500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>660000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>617000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>583200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>537000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>473600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>451700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>517200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>554400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>522100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>574800</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>581800</v>
+      </c>
+      <c r="E45" s="3">
         <v>704400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>530100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>764700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1035300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1225800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>926500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1086800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>753500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1086800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>753500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>869400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>181700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>184100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>183400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>145900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>146100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>149000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>142900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>132200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>143200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>144700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>161900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>191900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>219300</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3820500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4092400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4236200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4268200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4228600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4206800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4532400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4073400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4169800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4073400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4169800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4355800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4286700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4104500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4342700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3851100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3763000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3709900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3805200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3554400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3598800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3501000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3774400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3655500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3762900</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1231400</v>
+      </c>
+      <c r="E47" s="3">
         <v>1223000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1244400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1007200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>781700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>789800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>706000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>688400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>683400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>688400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>683400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>706100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>471100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>440400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>399900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>377400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>459000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>389400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>368500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>321000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>283200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>294800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>369200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>387300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>381300</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1715500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1758700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1919700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1865100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1854000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1926200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2026000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1959700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1998500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1959700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1998500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2061800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1928800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1809300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1986300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1885400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1866500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1924000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1961500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1881800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1897100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2009500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2227900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2416100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2503000</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>700200</v>
+      </c>
+      <c r="E49" s="3">
         <v>619000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>652900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>643000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>634100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>651100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>679100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>666600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>665500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>666600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>665500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>687100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>642700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>609600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>633700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>597800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>586700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>637900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>664400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>655900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>659700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>696400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>781000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>788500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>829600</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3690,8 +3804,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3767,16 +3884,19 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>10</v>
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>10</v>
@@ -3784,14 +3904,14 @@
       <c r="G52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>10</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>10</v>
@@ -3805,47 +3925,50 @@
       <c r="N52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P52" s="3">
         <v>120200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>107500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>115600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>106900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>109900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>112600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>115500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>105700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>109900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>115200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>127300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>127200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3921,85 +4044,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7576100</v>
+      </c>
+      <c r="E54" s="3">
         <v>7801500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8167000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7886900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7591000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7666500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8042100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7489400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7623500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7489400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7623500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7920700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7449400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7071200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7478300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6818700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6785200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6773900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6915100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6518800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6548700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6616900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7279800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7374600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7611900</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4027,8 +4156,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4056,470 +4186,489 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1250700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1413300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1477100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1471800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1322200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1273600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1198000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1123400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1182200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1123400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1182200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1230800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>907900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1173700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1214100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1067200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>834900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1094200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1193800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1033800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>742900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1040800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1261400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1214700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1321600</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E58" s="3">
         <v>22200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>67000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>133500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>157100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>82100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>106200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>81800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>116300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>81800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>116300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>94200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>121100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>237200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>255000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>260700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>269800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>97500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>119100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>87000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>107800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>81600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>55300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>50200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>137100</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E59" s="3">
         <v>223100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>281000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>291600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>404700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>344000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>293800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>499800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>503900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>499800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>503900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>509800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>793300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>485500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>527200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>477600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>780700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>482800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>508600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>449000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>858700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>494500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>536500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>484400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>451900</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1538400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1683400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1825100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1918200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1884000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1699700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1915900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1705000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1802400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1705000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1802400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1834800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1822300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1896400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1996300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1805500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1885500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1674400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1821600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1569800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1709500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1616900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1853200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1749300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1910600</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>48300</v>
+        <v>39800</v>
       </c>
       <c r="E61" s="3">
         <v>48300</v>
       </c>
       <c r="F61" s="3">
+        <v>48300</v>
+      </c>
+      <c r="G61" s="3">
         <v>37300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>95600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>96400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>122100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>124300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>122100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>124300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>124600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>284400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>113100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>114900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>30900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>248600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>175700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>179300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>172800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>435100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>196800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>240600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>242000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>590200</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>228900</v>
+      </c>
+      <c r="E62" s="3">
         <v>186000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>206500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>199000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>205500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>219100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>222400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>209400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>224600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>209400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>224600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>214400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>311600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>436300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>535800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>515000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>285700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>535700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>541700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>546200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>279900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>574500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>626100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>683700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>328100</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4595,8 +4744,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4672,8 +4824,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4749,85 +4904,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1996200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2117000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2254200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2329600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2332100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2243400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2450100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2331900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2438100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2331900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2438100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2465800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3055400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3048700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3246000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2913800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2954200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2920600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3059800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2817700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2935000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2906800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3271700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3268400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3444100</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4855,8 +5016,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4932,8 +5094,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5009,8 +5174,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5086,8 +5254,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5163,85 +5334,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5087200</v>
+      </c>
+      <c r="E72" s="3">
         <v>5111200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5515700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4874300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4590600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4738900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5042400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4571700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4622200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4571700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4622200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4890200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4578500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4017500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4181000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4024700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4122900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4247700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4248500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3957500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4014600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4174400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4470400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4615900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4531600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5317,8 +5494,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5394,8 +5574,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5471,85 +5654,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4993000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5068700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5288100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4917100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4653600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4768300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4935500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4534500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4573200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4534500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4573200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4762300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4394100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4022500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4232200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3904800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3831000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3853300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3855300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3701100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3613700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3710100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4008100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4106200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4167800</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5625,90 +5814,96 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5745,47 +5940,50 @@
       <c r="N81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P81" s="3">
         <v>107500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>132100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>100700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>111700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>74200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>158500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>146000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>142500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>89900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>162000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>169300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5813,85 +6011,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>72500</v>
+      </c>
+      <c r="E83" s="3">
         <v>73600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>74300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>71300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>77800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>85400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>70000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>76700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>70000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>76700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>79800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>80000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>64600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>70200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>64300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>65800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>68900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>70400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>65300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>66400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>69700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>75700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>81800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>85300</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5967,8 +6169,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6044,8 +6249,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6121,8 +6329,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6198,8 +6409,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6275,85 +6489,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>195400</v>
+      </c>
+      <c r="E89" s="3">
         <v>264400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>213800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>190500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>179000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>279300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>341200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>224100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>261800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>224100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>261800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>323400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>174300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>116200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>167800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>163000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>171000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>135500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>288200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>158600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>322600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>244700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>260800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>389800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>240200</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6381,85 +6601,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-39600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-47700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-79300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-74300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-82100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-82100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-55800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-57200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9529000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8001000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8738000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6682000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9393000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9395000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-66700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-48300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-75100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-74300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-67700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-69700</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6535,8 +6759,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6612,85 +6839,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-90500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-234200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>109800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-525700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>160800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-423900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>11900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-423900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>11900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-215100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>83500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-91700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-108400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>76700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-183500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-194500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-142800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-47600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-183300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>28700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-64600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-112700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-238900</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6718,8 +6951,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6735,18 +6969,18 @@
       <c r="G96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3">
         <v>78100</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3">
         <v>79300</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
@@ -6756,47 +6990,50 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P96" s="3">
         <v>100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-72300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-71300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-77400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-68000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-74500</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-73600</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6872,8 +7109,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6949,8 +7189,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7026,235 +7269,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-39800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-127600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-173400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-123600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-183500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-162800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-183500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-162800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-101800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-240200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-157400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>28200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-48800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-148300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-107200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-64700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-31400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-111000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-103200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>201000</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E101" s="3">
         <v>26100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-21600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>14200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>48800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>19700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-62900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>12100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>42300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>42300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>57600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-58900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>11100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>38700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>46500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>23400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>31300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>13000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-54800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>56400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-34700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>129900</v>
+      </c>
+      <c r="E102" s="3">
         <v>180900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-150800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>241400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>171600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-343900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>462400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-369100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>159700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-369100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>159700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-121700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>126400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>237300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-206600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>37200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>77600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>120900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>107600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>210000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>139200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>226300</v>
       </c>
     </row>
